--- a/artfynd/S 1548-2026 artfynd.xlsx
+++ b/artfynd/S 1548-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY21"/>
+  <dimension ref="A1:AZ21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -783,6 +788,11 @@
           <t>Hammarö Kommun - NVI Hammarö</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130795387</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -910,6 +920,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130334533</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1025,6 +1040,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109650891</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1126,6 +1146,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119630601</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1237,6 +1262,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109757667</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1352,6 +1382,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115991640</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1459,6 +1494,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118612098</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1576,6 +1616,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118614472</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1691,6 +1736,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115990902</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1810,6 +1860,11 @@
       <c r="AY11" t="inlineStr">
         <is>
           <t>Hammarö Kommun - NVI Hammarö</t>
+        </is>
+      </c>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130795401</t>
         </is>
       </c>
     </row>
@@ -1927,6 +1982,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109534139</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -2047,6 +2107,11 @@
           <t>Hammarö Kommun - NVI Hammarö</t>
         </is>
       </c>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130795441</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2172,6 +2237,11 @@
           <t>Hammarö Kommun - NVI Hammarö</t>
         </is>
       </c>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130795354</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2297,6 +2367,11 @@
           <t>Hammarö Kommun - NVI Hammarö</t>
         </is>
       </c>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130795375</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2422,6 +2497,11 @@
           <t>Hammarö Kommun - NVI Hammarö</t>
         </is>
       </c>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130795381</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2547,6 +2627,11 @@
           <t>Hammarö Kommun - NVI Hammarö</t>
         </is>
       </c>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130795382</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2672,6 +2757,11 @@
           <t>Hammarö Kommun - NVI Hammarö</t>
         </is>
       </c>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130795370</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2797,6 +2887,11 @@
           <t>Hammarö Kommun - NVI Hammarö</t>
         </is>
       </c>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130795371</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2922,6 +3017,11 @@
           <t>Hammarö Kommun - NVI Hammarö</t>
         </is>
       </c>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130795411</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -3047,8 +3147,35 @@
           <t>Hammarö Kommun - NVI Hammarö</t>
         </is>
       </c>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130795412</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>